--- a/health_coach_forms/001_longevity_protocol_intake_form--health_coach_forms.xlsx
+++ b/health_coach_forms/001_longevity_protocol_intake_form--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>longivity_protocol_intake_form_first_page</t>
+          <t>longevity_protocol_intake_form_first_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Page</t>
+          <t>What is your current weight?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_second_page</t>
+          <t>longevity_protocol_intake_form_exercise_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Second Page</t>
+          <t>How often do you exercise?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_third_page</t>
+          <t>longevity_protocol_intake_form_sleep_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Third Page</t>
+          <t>How many hours do you sleep each night?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_fourth_page</t>
+          <t>longevity_protocol_intake_form_diet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fourth Page</t>
+          <t>What is your average monthly diet?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_fifth_page</t>
+          <t>longevity_protocol_intake_form_health_insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fifth Page</t>
+          <t>Do you have any health insurance?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_sixth_page</t>
+          <t>longevity_protocol_intake_form_social_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sixth Page</t>
+          <t>How much time do you spend on social media each day?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_seventh_page</t>
+          <t>longevity_protocol_intake_form_fruits_vegetables</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seventh Page</t>
+          <t>How many servings of fruits and vegetables do you consume daily?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_eighth_page</t>
+          <t>longevity_protocol_intake_form_chronic_conditions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eighth Page</t>
+          <t>Do you have any chronic health conditions?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_ninth_page</t>
+          <t>longevity_protocol_intake_form_tv_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ninth Page</t>
+          <t>How many hours do you spend watching TV each day?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_tenth_page</t>
+          <t>longevity_protocol_intake_form_water_intake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tenth Page</t>
+          <t>What is your average daily water intake?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_eleventh_page</t>
+          <t>longevity_protocol_intake_form_eating_out</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eleventh Page</t>
+          <t>How many times do you eat out per week?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_twelfth_page</t>
+          <t>longevity_protocol_intake_form_allergies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Twelfth Page</t>
+          <t>Do you have any allergies?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_thirteenth_page</t>
+          <t>longevity_protocol_intake_form_work_hours</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thirteenth Page</t>
+          <t>How many hours do you spend on work-related tasks each day?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_fourteenth_page</t>
+          <t>longevity_protocol_intake_form_stress_level</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fourteenth Page</t>
+          <t>What is your average stress level on a scale of 1-10?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_fifth_page</t>
+          <t>longevity_protocol_intake_form_relaxation_hours</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fifth Page</t>
+          <t>How many hours do you spend on relaxation activities each day?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_sixth_page</t>
+          <t>longevity_protocol_intake_form_sleep_conditions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sixth Page</t>
+          <t>Do you have any medical conditions that affect your sleep?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_seventh_page</t>
+          <t>longevity_protocol_intake_form_protein_intake</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seventh Page</t>
+          <t>How many servings of lean protein do you consume daily?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_eighth_page</t>
+          <t>longevity_protocol_intake_form_hobbies_hours</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eighth Page</t>
+          <t>How many hours do you spend on hobbies each day?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_ninth_page</t>
+          <t>longevity_protocol_intake_form_note</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ninth Page</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_tenth_page</t>
+          <t>longevity_protocol_intake_form_email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tenth Page</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,568 +980,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_eleventh_page</t>
+          <t>longevity_protocol_intake_form_phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eleventh Page</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_twelfth_page</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Twelfth Page</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_thirteenth_page</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thirteenth Page</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_fourteenth_page</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Fourteenth Page</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_fifth_page</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fifth Page</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_select_one</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_select_multiple</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_date</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_time</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_note</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_email</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_phone</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_text</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_integer</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_decimal</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_text_area</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Text Area</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_email</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_phone</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_integer</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_decimal</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_note</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_text</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_time</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_integer</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>longevity_protocol_intake_form_decimal</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1558,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1586,102 +1034,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_select_one_choices</t>
+          <t>longevity_protocol_intake_form_exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_select_one_choices</t>
+          <t>longevity_protocol_intake_form_exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_select_one_choices</t>
+          <t>longevity_protocol_intake_form_exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_select_multiple_choices</t>
+          <t>longevity_protocol_intake_form_diet_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_select_multiple_choices</t>
+          <t>longevity_protocol_intake_form_diet_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>longevity_protocol_intake_form_select_multiple_choices</t>
+          <t>longevity_protocol_intake_form_diet_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>longevity_protocol_intake_form_health_insurance_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>longevity_protocol_intake_form_health_insurance_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>longevity_protocol_intake_form_health_insurance_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>longevity_protocol_intake_form_water_intake_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>longevity_protocol_intake_form_water_intake_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>longevity_protocol_intake_form_water_intake_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
